--- a/data/tags.xlsx
+++ b/data/tags.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vogelwarte-my.sharepoint.com/personal/raphael_nussbaumer_vogelwarte_ch/Documents/2-geolocator_data/SwissHoopoe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_C6B33FD58F79A8D366075C52F37BD2727A4B8D4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DCE1A32-F89E-204C-A1AA-18B0F74A81B2}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_C6B33FD58F79A8D366075C52F37BD2727A4B8D4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4687C83-CBC3-1345-B705-C3F08F5AEBD5}"/>
   <bookViews>
-    <workbookView xWindow="15340" yWindow="6480" windowWidth="34420" windowHeight="22140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="760" windowWidth="27200" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8687" uniqueCount="2281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8698" uniqueCount="2295">
   <si>
     <t>tag_id</t>
   </si>
@@ -6864,13 +6877,55 @@
     <t>H117895</t>
   </si>
   <si>
-    <t>16cl</t>
-  </si>
-  <si>
     <t>H122809</t>
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>6HW</t>
+  </si>
+  <si>
+    <t>6HY</t>
+  </si>
+  <si>
+    <t>6HU</t>
+  </si>
+  <si>
+    <t>6HE</t>
+  </si>
+  <si>
+    <t>6HC</t>
+  </si>
+  <si>
+    <t>6GY</t>
+  </si>
+  <si>
+    <t>British Antarctic Survey</t>
+  </si>
+  <si>
+    <t>16CL</t>
+  </si>
+  <si>
+    <t>GDL1-v1.2</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>19AB</t>
+  </si>
+  <si>
+    <t>19AE</t>
+  </si>
+  <si>
+    <t>FL27809</t>
+  </si>
+  <si>
+    <t>Austria. Storage full on 17.12.2015</t>
+  </si>
+  <si>
+    <t>Austria. light blue color ring with number "81" ring from Radolfzell with number "FL27809"</t>
   </si>
 </sst>
 </file>
@@ -6894,15 +6949,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -6910,20 +6971,144 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6934,6 +7119,29 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52C881B9-7809-A748-8C7C-372F5941B8CE}" name="Table1" displayName="Table1" ref="A1:J1210" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J1210" xr:uid="{52C881B9-7809-A748-8C7C-372F5941B8CE}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{35C276C1-1E72-684F-903F-CD896DE0DF94}" name="tag_id" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A0CFFD9E-0215-8F46-A48E-0134E95FF4E9}" name="ring_number" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B756B87A-F700-0547-944F-4414375E6FA4}" name="scientific_name"/>
+    <tableColumn id="4" xr3:uid="{EB44EB47-6A68-1345-8585-DEF831E3E9D6}" name="manufacturer"/>
+    <tableColumn id="5" xr3:uid="{66EF5376-FD28-124E-9BBD-CD1AC838E789}" name="model"/>
+    <tableColumn id="6" xr3:uid="{F1DE16DE-0EA9-674E-83C0-C34DA0A8806D}" name="firwmare"/>
+    <tableColumn id="7" xr3:uid="{C2CCF05D-2E58-E346-974C-0D8BC1CEA242}" name="weight"/>
+    <tableColumn id="8" xr3:uid="{E366D6AD-AC04-2E47-B8F2-1F23DDFE27BA}" name="attachment_type"/>
+    <tableColumn id="9" xr3:uid="{9D8044AD-F072-0E40-9C4C-779769166DB1}" name="readout_method"/>
+    <tableColumn id="10" xr3:uid="{5676D58C-FF64-0C46-954B-01017967241C}" name="tag_comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7223,8 +7431,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1202"/>
+  <dimension ref="A1:J1210"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -8959,7 +9176,7 @@
         <v>172</v>
       </c>
       <c r="F76" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G76">
         <v>1.3</v>
@@ -8985,7 +9202,7 @@
         <v>172</v>
       </c>
       <c r="F77" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G77">
         <v>1.23</v>
@@ -9037,7 +9254,7 @@
         <v>172</v>
       </c>
       <c r="F79" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G79">
         <v>1.23</v>
@@ -9089,7 +9306,7 @@
         <v>172</v>
       </c>
       <c r="F81" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G81">
         <v>1.25</v>
@@ -9167,7 +9384,7 @@
         <v>172</v>
       </c>
       <c r="F84" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G84">
         <v>1.25</v>
@@ -9219,7 +9436,7 @@
         <v>172</v>
       </c>
       <c r="F86" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G86">
         <v>1.24</v>
@@ -9245,7 +9462,7 @@
         <v>172</v>
       </c>
       <c r="F87" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G87">
         <v>1.25</v>
@@ -9271,7 +9488,7 @@
         <v>172</v>
       </c>
       <c r="F88" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G88">
         <v>1.24</v>
@@ -9297,7 +9514,7 @@
         <v>172</v>
       </c>
       <c r="F89" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G89">
         <v>1.26</v>
@@ -9323,7 +9540,7 @@
         <v>172</v>
       </c>
       <c r="F90" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G90">
         <v>1.25</v>
@@ -9349,7 +9566,7 @@
         <v>172</v>
       </c>
       <c r="F91" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G91">
         <v>1.24</v>
@@ -9375,7 +9592,7 @@
         <v>172</v>
       </c>
       <c r="F92" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G92">
         <v>1.24</v>
@@ -9401,7 +9618,7 @@
         <v>172</v>
       </c>
       <c r="F93" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G93">
         <v>1.22</v>
@@ -9427,7 +9644,7 @@
         <v>172</v>
       </c>
       <c r="F94" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G94">
         <v>1.23</v>
@@ -9453,7 +9670,7 @@
         <v>172</v>
       </c>
       <c r="F95" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G95">
         <v>1.25</v>
@@ -9479,7 +9696,7 @@
         <v>172</v>
       </c>
       <c r="F96" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G96">
         <v>1.23</v>
@@ -9505,7 +9722,7 @@
         <v>172</v>
       </c>
       <c r="F97" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G97">
         <v>1.23</v>
@@ -9531,7 +9748,7 @@
         <v>172</v>
       </c>
       <c r="F98" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G98">
         <v>1.22</v>
@@ -9557,7 +9774,7 @@
         <v>172</v>
       </c>
       <c r="F99" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G99">
         <v>1.26</v>
@@ -9583,7 +9800,7 @@
         <v>172</v>
       </c>
       <c r="F100" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G100">
         <v>1.27</v>
@@ -9609,7 +9826,7 @@
         <v>172</v>
       </c>
       <c r="F101" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G101">
         <v>1.25</v>
@@ -9635,7 +9852,7 @@
         <v>172</v>
       </c>
       <c r="F102" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G102">
         <v>1.24</v>
@@ -9687,7 +9904,7 @@
         <v>172</v>
       </c>
       <c r="F104" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G104">
         <v>1.23</v>
@@ -9713,7 +9930,7 @@
         <v>172</v>
       </c>
       <c r="F105" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G105">
         <v>1.24</v>
@@ -9739,7 +9956,7 @@
         <v>172</v>
       </c>
       <c r="F106" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G106">
         <v>1.25</v>
@@ -9765,7 +9982,7 @@
         <v>172</v>
       </c>
       <c r="F107" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G107">
         <v>1.24</v>
@@ -10051,7 +10268,7 @@
         <v>172</v>
       </c>
       <c r="F118" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G118">
         <v>1.25</v>
@@ -10077,7 +10294,7 @@
         <v>172</v>
       </c>
       <c r="F119" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G119">
         <v>1.24</v>
@@ -10389,7 +10606,7 @@
         <v>172</v>
       </c>
       <c r="F131" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G131">
         <v>1.33</v>
@@ -10415,7 +10632,7 @@
         <v>172</v>
       </c>
       <c r="F132" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G132">
         <v>1.35</v>
@@ -10441,7 +10658,7 @@
         <v>172</v>
       </c>
       <c r="F133" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G133">
         <v>1.34</v>
@@ -10467,7 +10684,7 @@
         <v>172</v>
       </c>
       <c r="F134" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G134">
         <v>1.37</v>
@@ -10493,7 +10710,7 @@
         <v>172</v>
       </c>
       <c r="F135" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G135">
         <v>1.34</v>
@@ -10519,7 +10736,7 @@
         <v>172</v>
       </c>
       <c r="F136" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G136">
         <v>1.3200000999999999</v>
@@ -10545,7 +10762,7 @@
         <v>172</v>
       </c>
       <c r="F137" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G137">
         <v>1.33</v>
@@ -10571,7 +10788,7 @@
         <v>172</v>
       </c>
       <c r="F138" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G138">
         <v>1.33</v>
@@ -10597,7 +10814,7 @@
         <v>172</v>
       </c>
       <c r="F139" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G139">
         <v>1.3099999</v>
@@ -10623,7 +10840,7 @@
         <v>172</v>
       </c>
       <c r="F140" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G140">
         <v>1.3200000999999999</v>
@@ -10649,7 +10866,7 @@
         <v>172</v>
       </c>
       <c r="F141" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G141">
         <v>1.3099999</v>
@@ -10675,7 +10892,7 @@
         <v>172</v>
       </c>
       <c r="F142" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G142">
         <v>1.3</v>
@@ -10701,7 +10918,7 @@
         <v>172</v>
       </c>
       <c r="F143" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G143">
         <v>1.35</v>
@@ -10727,7 +10944,7 @@
         <v>172</v>
       </c>
       <c r="F144" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G144">
         <v>1.29</v>
@@ -10753,7 +10970,7 @@
         <v>172</v>
       </c>
       <c r="F145" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G145">
         <v>1.3200000999999999</v>
@@ -10779,7 +10996,7 @@
         <v>172</v>
       </c>
       <c r="F146" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G146">
         <v>1.34</v>
@@ -10805,7 +11022,7 @@
         <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G147">
         <v>1.28</v>
@@ -10831,7 +11048,7 @@
         <v>172</v>
       </c>
       <c r="F148" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G148">
         <v>1.3</v>
@@ -10857,7 +11074,7 @@
         <v>172</v>
       </c>
       <c r="F149" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G149">
         <v>1.33</v>
@@ -10883,7 +11100,7 @@
         <v>172</v>
       </c>
       <c r="F150" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G150">
         <v>1.3</v>
@@ -10909,7 +11126,7 @@
         <v>172</v>
       </c>
       <c r="F151" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G151">
         <v>1.3200000999999999</v>
@@ -10935,7 +11152,7 @@
         <v>172</v>
       </c>
       <c r="F152" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G152">
         <v>1.35</v>
@@ -10961,7 +11178,7 @@
         <v>172</v>
       </c>
       <c r="F153" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G153">
         <v>1.3200000999999999</v>
@@ -10987,7 +11204,7 @@
         <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G154">
         <v>1.35</v>
@@ -11013,7 +11230,7 @@
         <v>172</v>
       </c>
       <c r="F155" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G155">
         <v>1.37</v>
@@ -11039,7 +11256,7 @@
         <v>172</v>
       </c>
       <c r="F156" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G156">
         <v>1.34</v>
@@ -11065,7 +11282,7 @@
         <v>172</v>
       </c>
       <c r="F157" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G157">
         <v>1.34</v>
@@ -11091,7 +11308,7 @@
         <v>172</v>
       </c>
       <c r="F158" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G158">
         <v>1.35</v>
@@ -11117,7 +11334,7 @@
         <v>172</v>
       </c>
       <c r="F159" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G159">
         <v>1.3200000999999999</v>
@@ -11143,7 +11360,7 @@
         <v>172</v>
       </c>
       <c r="F160" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G160">
         <v>1.35</v>
@@ -11169,7 +11386,7 @@
         <v>172</v>
       </c>
       <c r="F161" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G161">
         <v>1.35</v>
@@ -11195,7 +11412,7 @@
         <v>172</v>
       </c>
       <c r="F162" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G162">
         <v>1.33</v>
@@ -11221,7 +11438,7 @@
         <v>172</v>
       </c>
       <c r="F163" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G163">
         <v>1.34</v>
@@ -11247,7 +11464,7 @@
         <v>172</v>
       </c>
       <c r="F164" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G164">
         <v>1.36</v>
@@ -11273,7 +11490,7 @@
         <v>172</v>
       </c>
       <c r="F165" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G165">
         <v>1.3</v>
@@ -11299,7 +11516,7 @@
         <v>172</v>
       </c>
       <c r="F166" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G166">
         <v>1.3099999</v>
@@ -11325,7 +11542,7 @@
         <v>172</v>
       </c>
       <c r="F167" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G167">
         <v>1.37</v>
@@ -11351,7 +11568,7 @@
         <v>172</v>
       </c>
       <c r="F168" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G168">
         <v>1.29</v>
@@ -11377,7 +11594,7 @@
         <v>172</v>
       </c>
       <c r="F169" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G169">
         <v>1.34</v>
@@ -11403,7 +11620,7 @@
         <v>172</v>
       </c>
       <c r="F170" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G170">
         <v>1.3</v>
@@ -11429,7 +11646,7 @@
         <v>172</v>
       </c>
       <c r="F171" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G171">
         <v>1.3200000999999999</v>
@@ -11455,7 +11672,7 @@
         <v>172</v>
       </c>
       <c r="F172" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G172">
         <v>1.36</v>
@@ -11481,7 +11698,7 @@
         <v>172</v>
       </c>
       <c r="F173" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G173">
         <v>1.33</v>
@@ -11507,7 +11724,7 @@
         <v>172</v>
       </c>
       <c r="F174" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G174">
         <v>1.33</v>
@@ -11533,7 +11750,7 @@
         <v>172</v>
       </c>
       <c r="F175" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G175">
         <v>1.34</v>
@@ -11559,7 +11776,7 @@
         <v>172</v>
       </c>
       <c r="F176" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G176">
         <v>1.35</v>
@@ -16895,7 +17112,7 @@
         <v>750</v>
       </c>
       <c r="F378" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G378">
         <v>1.37</v>
@@ -16918,7 +17135,7 @@
         <v>750</v>
       </c>
       <c r="F379" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G379">
         <v>1.3</v>
@@ -16941,7 +17158,7 @@
         <v>750</v>
       </c>
       <c r="F380" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G380">
         <v>1.34</v>
@@ -16964,7 +17181,7 @@
         <v>750</v>
       </c>
       <c r="F381" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G381">
         <v>1.34</v>
@@ -16987,7 +17204,7 @@
         <v>750</v>
       </c>
       <c r="F382" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G382">
         <v>1.37</v>
@@ -17010,7 +17227,7 @@
         <v>750</v>
       </c>
       <c r="F383" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G383">
         <v>1.37</v>
@@ -17033,7 +17250,7 @@
         <v>750</v>
       </c>
       <c r="F384" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G384">
         <v>1.35</v>
@@ -17056,7 +17273,7 @@
         <v>750</v>
       </c>
       <c r="F385" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G385">
         <v>1.4299999000000001</v>
@@ -17079,7 +17296,7 @@
         <v>750</v>
       </c>
       <c r="F386" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G386">
         <v>1.38</v>
@@ -17102,7 +17319,7 @@
         <v>750</v>
       </c>
       <c r="F387" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G387">
         <v>1.37</v>
@@ -17125,7 +17342,7 @@
         <v>750</v>
       </c>
       <c r="F388" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G388">
         <v>1.41</v>
@@ -17148,7 +17365,7 @@
         <v>750</v>
       </c>
       <c r="F389" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G389">
         <v>1.37</v>
@@ -17171,7 +17388,7 @@
         <v>750</v>
       </c>
       <c r="F390" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G390">
         <v>1.37</v>
@@ -17194,7 +17411,7 @@
         <v>750</v>
       </c>
       <c r="F391" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G391">
         <v>1.34</v>
@@ -17217,7 +17434,7 @@
         <v>750</v>
       </c>
       <c r="F392" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G392">
         <v>1.35</v>
@@ -17240,7 +17457,7 @@
         <v>750</v>
       </c>
       <c r="F393" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G393">
         <v>1.34</v>
@@ -17263,7 +17480,7 @@
         <v>750</v>
       </c>
       <c r="F394" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G394">
         <v>1.37</v>
@@ -17286,7 +17503,7 @@
         <v>750</v>
       </c>
       <c r="F395" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G395">
         <v>1.35</v>
@@ -17309,7 +17526,7 @@
         <v>750</v>
       </c>
       <c r="F396" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G396">
         <v>1.3</v>
@@ -17332,7 +17549,7 @@
         <v>750</v>
       </c>
       <c r="F397" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G397">
         <v>1.36</v>
@@ -17355,7 +17572,7 @@
         <v>750</v>
       </c>
       <c r="F398" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G398">
         <v>1.37</v>
@@ -17378,7 +17595,7 @@
         <v>750</v>
       </c>
       <c r="F399" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G399">
         <v>1.37</v>
@@ -17401,7 +17618,7 @@
         <v>750</v>
       </c>
       <c r="F400" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G400">
         <v>1.33</v>
@@ -17424,7 +17641,7 @@
         <v>750</v>
       </c>
       <c r="F401" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G401">
         <v>1.35</v>
@@ -17447,7 +17664,7 @@
         <v>750</v>
       </c>
       <c r="F402" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G402">
         <v>1.33</v>
@@ -17470,7 +17687,7 @@
         <v>750</v>
       </c>
       <c r="F403" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G403">
         <v>1.39</v>
@@ -17493,7 +17710,7 @@
         <v>750</v>
       </c>
       <c r="F404" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G404">
         <v>1.34</v>
@@ -17516,7 +17733,7 @@
         <v>750</v>
       </c>
       <c r="F405" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G405">
         <v>1.34</v>
@@ -17539,7 +17756,7 @@
         <v>750</v>
       </c>
       <c r="F406" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G406">
         <v>1.41</v>
@@ -17562,7 +17779,7 @@
         <v>750</v>
       </c>
       <c r="F407" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G407">
         <v>1.36</v>
@@ -17585,7 +17802,7 @@
         <v>750</v>
       </c>
       <c r="F408" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G408">
         <v>1.36</v>
@@ -17608,7 +17825,7 @@
         <v>750</v>
       </c>
       <c r="F409" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G409">
         <v>1.39</v>
@@ -17631,7 +17848,7 @@
         <v>750</v>
       </c>
       <c r="F410" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G410">
         <v>1.36</v>
@@ -17654,7 +17871,7 @@
         <v>750</v>
       </c>
       <c r="F411" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G411">
         <v>1.3200000999999999</v>
@@ -17677,7 +17894,7 @@
         <v>750</v>
       </c>
       <c r="F412" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G412">
         <v>1.33</v>
@@ -17700,7 +17917,7 @@
         <v>750</v>
       </c>
       <c r="F413" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G413">
         <v>1.34</v>
@@ -17723,7 +17940,7 @@
         <v>750</v>
       </c>
       <c r="F414" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G414">
         <v>1.36</v>
@@ -17749,7 +17966,7 @@
         <v>750</v>
       </c>
       <c r="F415" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G415">
         <v>1.36</v>
@@ -17772,7 +17989,7 @@
         <v>750</v>
       </c>
       <c r="F416" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G416">
         <v>1.33</v>
@@ -17795,7 +18012,7 @@
         <v>750</v>
       </c>
       <c r="F417" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G417">
         <v>1.36</v>
@@ -17818,7 +18035,7 @@
         <v>750</v>
       </c>
       <c r="F418" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G418">
         <v>1.35</v>
@@ -17841,7 +18058,7 @@
         <v>750</v>
       </c>
       <c r="F419" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G419">
         <v>1.36</v>
@@ -17864,7 +18081,7 @@
         <v>750</v>
       </c>
       <c r="F420" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G420">
         <v>1.3099999</v>
@@ -17887,7 +18104,7 @@
         <v>750</v>
       </c>
       <c r="F421" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G421">
         <v>1.46</v>
@@ -17910,7 +18127,7 @@
         <v>750</v>
       </c>
       <c r="F422" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G422">
         <v>1.38</v>
@@ -17933,7 +18150,7 @@
         <v>750</v>
       </c>
       <c r="F423" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G423">
         <v>1.36</v>
@@ -17956,7 +18173,7 @@
         <v>750</v>
       </c>
       <c r="F424" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G424">
         <v>1.38</v>
@@ -17979,7 +18196,7 @@
         <v>750</v>
       </c>
       <c r="F425" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G425">
         <v>1.45</v>
@@ -18002,7 +18219,7 @@
         <v>750</v>
       </c>
       <c r="F426" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G426">
         <v>1.39</v>
@@ -18025,7 +18242,7 @@
         <v>750</v>
       </c>
       <c r="F427" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G427">
         <v>1.39</v>
@@ -18048,7 +18265,7 @@
         <v>750</v>
       </c>
       <c r="F428" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G428">
         <v>1.39</v>
@@ -18071,7 +18288,7 @@
         <v>750</v>
       </c>
       <c r="F429" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G429">
         <v>1.4400001</v>
@@ -18094,7 +18311,7 @@
         <v>750</v>
       </c>
       <c r="F430" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G430">
         <v>1.4299999000000001</v>
@@ -18117,7 +18334,7 @@
         <v>750</v>
       </c>
       <c r="F431" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G431">
         <v>1.38</v>
@@ -18140,7 +18357,7 @@
         <v>750</v>
       </c>
       <c r="F432" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G432">
         <v>1.41</v>
@@ -38141,7 +38358,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="1153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1153" t="s">
         <v>2191</v>
       </c>
@@ -38151,14 +38368,11 @@
       <c r="C1153" t="s">
         <v>12</v>
       </c>
-      <c r="E1153" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1153" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1153" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1154" t="s">
         <v>2193</v>
       </c>
@@ -38168,14 +38382,11 @@
       <c r="C1154" t="s">
         <v>12</v>
       </c>
-      <c r="E1154" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1154" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1154" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1155" t="s">
         <v>2195</v>
       </c>
@@ -38185,14 +38396,11 @@
       <c r="C1155" t="s">
         <v>12</v>
       </c>
-      <c r="E1155" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1155" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1155" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1156" t="s">
         <v>2197</v>
       </c>
@@ -38202,14 +38410,11 @@
       <c r="C1156" t="s">
         <v>12</v>
       </c>
-      <c r="E1156" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1156" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1156" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1157" t="s">
         <v>2199</v>
       </c>
@@ -38219,14 +38424,11 @@
       <c r="C1157" t="s">
         <v>12</v>
       </c>
-      <c r="E1157" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1157" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1157" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1158" t="s">
         <v>2201</v>
       </c>
@@ -38236,14 +38438,11 @@
       <c r="C1158" t="s">
         <v>12</v>
       </c>
-      <c r="E1158" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1158" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1158" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1159" t="s">
         <v>2203</v>
       </c>
@@ -38253,14 +38452,11 @@
       <c r="C1159" t="s">
         <v>12</v>
       </c>
-      <c r="E1159" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1159" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1159" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1160" t="s">
         <v>2205</v>
       </c>
@@ -38270,14 +38466,11 @@
       <c r="C1160" t="s">
         <v>12</v>
       </c>
-      <c r="E1160" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1160" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1160" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1161" t="s">
         <v>2207</v>
       </c>
@@ -38287,14 +38480,11 @@
       <c r="C1161" t="s">
         <v>12</v>
       </c>
-      <c r="E1161" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1161" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1161" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1162" t="s">
         <v>2209</v>
       </c>
@@ -38304,14 +38494,11 @@
       <c r="C1162" t="s">
         <v>12</v>
       </c>
-      <c r="E1162" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1162" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1162" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1163" t="s">
         <v>2211</v>
       </c>
@@ -38321,14 +38508,11 @@
       <c r="C1163" t="s">
         <v>12</v>
       </c>
-      <c r="E1163" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1163" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1163" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1164" t="s">
         <v>2213</v>
       </c>
@@ -38338,14 +38522,11 @@
       <c r="C1164" t="s">
         <v>12</v>
       </c>
-      <c r="E1164" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1164" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1164" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1165" t="s">
         <v>2215</v>
       </c>
@@ -38355,14 +38536,11 @@
       <c r="C1165" t="s">
         <v>12</v>
       </c>
-      <c r="E1165" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1165" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1165" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1166" t="s">
         <v>2217</v>
       </c>
@@ -38372,14 +38550,11 @@
       <c r="C1166" t="s">
         <v>12</v>
       </c>
-      <c r="E1166" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1166" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1166" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1167" t="s">
         <v>2219</v>
       </c>
@@ -38389,14 +38564,11 @@
       <c r="C1167" t="s">
         <v>12</v>
       </c>
-      <c r="E1167" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1167" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1167" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1168" t="s">
         <v>2221</v>
       </c>
@@ -38406,14 +38578,11 @@
       <c r="C1168" t="s">
         <v>12</v>
       </c>
-      <c r="E1168" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1168" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1168" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1169" t="s">
         <v>2222</v>
       </c>
@@ -38423,14 +38592,11 @@
       <c r="C1169" t="s">
         <v>12</v>
       </c>
-      <c r="E1169" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1169" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1169" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1170" t="s">
         <v>2223</v>
       </c>
@@ -38440,14 +38606,11 @@
       <c r="C1170" t="s">
         <v>12</v>
       </c>
-      <c r="E1170" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1170" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1170" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1171" t="s">
         <v>2225</v>
       </c>
@@ -38457,14 +38620,11 @@
       <c r="C1171" t="s">
         <v>12</v>
       </c>
-      <c r="E1171" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1171" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1171" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1172" t="s">
         <v>2226</v>
       </c>
@@ -38474,14 +38634,11 @@
       <c r="C1172" t="s">
         <v>12</v>
       </c>
-      <c r="E1172" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1172" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1172" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1173" t="s">
         <v>2227</v>
       </c>
@@ -38491,14 +38648,11 @@
       <c r="C1173" t="s">
         <v>12</v>
       </c>
-      <c r="E1173" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1173" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1173" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1174" t="s">
         <v>2229</v>
       </c>
@@ -38508,14 +38662,11 @@
       <c r="C1174" t="s">
         <v>12</v>
       </c>
-      <c r="E1174" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1174" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1174" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1175" t="s">
         <v>2230</v>
       </c>
@@ -38525,14 +38676,11 @@
       <c r="C1175" t="s">
         <v>12</v>
       </c>
-      <c r="E1175" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1175" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1175" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1176" t="s">
         <v>2232</v>
       </c>
@@ -38542,14 +38690,11 @@
       <c r="C1176" t="s">
         <v>12</v>
       </c>
-      <c r="E1176" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1176" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1176" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1177" t="s">
         <v>2234</v>
       </c>
@@ -38559,14 +38704,11 @@
       <c r="C1177" t="s">
         <v>12</v>
       </c>
-      <c r="E1177" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1177" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1177" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1178" t="s">
         <v>2236</v>
       </c>
@@ -38576,14 +38718,11 @@
       <c r="C1178" t="s">
         <v>12</v>
       </c>
-      <c r="E1178" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1178" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1178" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1179" t="s">
         <v>2238</v>
       </c>
@@ -38593,14 +38732,11 @@
       <c r="C1179" t="s">
         <v>12</v>
       </c>
-      <c r="E1179" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1179" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1179" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1180" t="s">
         <v>2240</v>
       </c>
@@ -38610,14 +38746,11 @@
       <c r="C1180" t="s">
         <v>12</v>
       </c>
-      <c r="E1180" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1180" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1180" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1181" t="s">
         <v>2241</v>
       </c>
@@ -38627,14 +38760,11 @@
       <c r="C1181" t="s">
         <v>12</v>
       </c>
-      <c r="E1181" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1181" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1181" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1182" t="s">
         <v>2243</v>
       </c>
@@ -38644,14 +38774,11 @@
       <c r="C1182" t="s">
         <v>12</v>
       </c>
-      <c r="E1182" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1182" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1182" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1183" t="s">
         <v>2245</v>
       </c>
@@ -38661,14 +38788,11 @@
       <c r="C1183" t="s">
         <v>12</v>
       </c>
-      <c r="E1183" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1183" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1183" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1184" t="s">
         <v>2247</v>
       </c>
@@ -38678,14 +38802,11 @@
       <c r="C1184" t="s">
         <v>12</v>
       </c>
-      <c r="E1184" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1184" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1184" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1185" t="s">
         <v>2248</v>
       </c>
@@ -38695,14 +38816,11 @@
       <c r="C1185" t="s">
         <v>12</v>
       </c>
-      <c r="E1185" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1185" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1185" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1186" t="s">
         <v>2250</v>
       </c>
@@ -38712,14 +38830,11 @@
       <c r="C1186" t="s">
         <v>12</v>
       </c>
-      <c r="E1186" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1186" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1186" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1187" t="s">
         <v>2252</v>
       </c>
@@ -38729,14 +38844,11 @@
       <c r="C1187" t="s">
         <v>12</v>
       </c>
-      <c r="E1187" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1187" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1187" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1188" t="s">
         <v>2254</v>
       </c>
@@ -38746,14 +38858,11 @@
       <c r="C1188" t="s">
         <v>12</v>
       </c>
-      <c r="E1188" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1188" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1188" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1189" t="s">
         <v>2256</v>
       </c>
@@ -38763,14 +38872,11 @@
       <c r="C1189" t="s">
         <v>12</v>
       </c>
-      <c r="E1189" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1189" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1189" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1190" t="s">
         <v>2258</v>
       </c>
@@ -38780,14 +38886,11 @@
       <c r="C1190" t="s">
         <v>12</v>
       </c>
-      <c r="E1190" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1190" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1190" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1191" t="s">
         <v>2260</v>
       </c>
@@ -38797,14 +38900,11 @@
       <c r="C1191" t="s">
         <v>12</v>
       </c>
-      <c r="E1191" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1191" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1191" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1192" t="s">
         <v>2262</v>
       </c>
@@ -38814,14 +38914,11 @@
       <c r="C1192" t="s">
         <v>12</v>
       </c>
-      <c r="E1192" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1192" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1193" t="s">
         <v>2263</v>
       </c>
@@ -38831,14 +38928,11 @@
       <c r="C1193" t="s">
         <v>12</v>
       </c>
-      <c r="E1193" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1193" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1193" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1194" t="s">
         <v>2265</v>
       </c>
@@ -38848,14 +38942,11 @@
       <c r="C1194" t="s">
         <v>12</v>
       </c>
-      <c r="E1194" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1194" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1194" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1195" t="s">
         <v>2267</v>
       </c>
@@ -38865,14 +38956,11 @@
       <c r="C1195" t="s">
         <v>12</v>
       </c>
-      <c r="E1195" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1195" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1195" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1196" t="s">
         <v>2268</v>
       </c>
@@ -38882,14 +38970,11 @@
       <c r="C1196" t="s">
         <v>12</v>
       </c>
-      <c r="E1196" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1196" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1196" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1197" t="s">
         <v>2270</v>
       </c>
@@ -38899,14 +38984,11 @@
       <c r="C1197" t="s">
         <v>12</v>
       </c>
-      <c r="E1197" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1197" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1197" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1198" t="s">
         <v>2272</v>
       </c>
@@ -38916,14 +38998,11 @@
       <c r="C1198" t="s">
         <v>12</v>
       </c>
-      <c r="E1198" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1198" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1198" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1199" t="s">
         <v>2274</v>
       </c>
@@ -38933,14 +39012,11 @@
       <c r="C1199" t="s">
         <v>12</v>
       </c>
-      <c r="E1199" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1199" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1199" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1200" t="s">
         <v>2275</v>
       </c>
@@ -38950,14 +39026,11 @@
       <c r="C1200" t="s">
         <v>12</v>
       </c>
-      <c r="E1200" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1200" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D1200" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1201" t="s">
         <v>2276</v>
       </c>
@@ -38967,31 +39040,273 @@
       <c r="C1201" t="s">
         <v>12</v>
       </c>
-      <c r="E1201" t="s">
+      <c r="D1201" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1202" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>506</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>524</v>
+      </c>
+      <c r="G1202">
+        <v>1.4299999000000001</v>
+      </c>
+      <c r="H1202" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1202" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1203" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B1203" s="2">
+        <v>3387611</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1203">
+        <v>1.29</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1203" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1204" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1204" s="2">
+        <v>3387605</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1204">
+        <v>1.28</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1204" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1205" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1205" s="2">
+        <v>3387597</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1205">
+        <v>1.29</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1205" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1206" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1206" s="2">
+        <v>3387596</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1206">
+        <v>1.3099999</v>
+      </c>
+      <c r="H1206" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1206" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1207" s="3" t="s">
         <v>2280</v>
       </c>
-      <c r="F1201" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1202" t="s">
-        <v>2278</v>
-      </c>
-      <c r="B1202" t="s">
-        <v>2279</v>
-      </c>
-      <c r="C1202" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1202" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F1202" t="s">
-        <v>2280</v>
+      <c r="B1207" s="2">
+        <v>3387577</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1207">
+        <v>1.29</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1207" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1208" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B1208" s="4">
+        <v>3387585</v>
+      </c>
+      <c r="C1208" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1208" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1208" s="6" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F1208" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1208" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="H1208" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1208" s="6"/>
+      <c r="J1208" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1209" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>651</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1209">
+        <v>0.67000002000000003</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1209" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1210" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>651</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1210">
+        <v>0.69</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1210" s="7" t="s">
+        <v>2294</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>